--- a/server/data/imports/uber/uber.xlsx
+++ b/server/data/imports/uber/uber.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V39\server\data\imports\uber\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V41\server\data\imports\uber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A8B64F-F0F4-477B-9A5C-C8A8EB378F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE05D950-A558-4377-B115-713DFD3BE233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A100726-893B-4AF6-887A-6E8D99DEE1FA}"/>
   </bookViews>
@@ -468,7 +468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0258365A-ED26-4117-A724-7F37F5D696E5}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:N164"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -2774,6 +2774,76 @@
         <v>383</v>
       </c>
     </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B165">
+        <v>261</v>
+      </c>
+      <c r="C165">
+        <v>169</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="2">
+        <v>46212</v>
+      </c>
+      <c r="B166">
+        <v>135</v>
+      </c>
+      <c r="C166">
+        <v>162</v>
+      </c>
+      <c r="D166">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B167">
+        <v>74</v>
+      </c>
+      <c r="C167">
+        <v>754</v>
+      </c>
+      <c r="D167">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="2">
+        <v>46214</v>
+      </c>
+      <c r="B168">
+        <v>208</v>
+      </c>
+      <c r="C168">
+        <v>973</v>
+      </c>
+      <c r="D168">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="2">
+        <v>46215</v>
+      </c>
+      <c r="B169">
+        <v>455</v>
+      </c>
+      <c r="C169">
+        <v>500</v>
+      </c>
+      <c r="D169">
+        <v>1100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/server/data/imports/uber/uber.xlsx
+++ b/server/data/imports/uber/uber.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V41\server\data\imports\uber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE05D950-A558-4377-B115-713DFD3BE233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEBD26C-8E22-48DF-BD96-020889E1919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A100726-893B-4AF6-887A-6E8D99DEE1FA}"/>
   </bookViews>
@@ -468,7 +468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0258365A-ED26-4117-A724-7F37F5D696E5}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N171"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -2844,6 +2844,34 @@
         <v>1100</v>
       </c>
     </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B170">
+        <v>61</v>
+      </c>
+      <c r="C170">
+        <v>147</v>
+      </c>
+      <c r="D170">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B171">
+        <v>163</v>
+      </c>
+      <c r="C171">
+        <v>285</v>
+      </c>
+      <c r="D171">
+        <v>463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/server/data/imports/uber/uber.xlsx
+++ b/server/data/imports/uber/uber.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V41\server\data\imports\uber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEBD26C-8E22-48DF-BD96-020889E1919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBDD851-E1A9-4A1B-B52F-14F9545A1128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A100726-893B-4AF6-887A-6E8D99DEE1FA}"/>
   </bookViews>
@@ -468,7 +468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0258365A-ED26-4117-A724-7F37F5D696E5}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:N171"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -2872,6 +2872,20 @@
         <v>463</v>
       </c>
     </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B172">
+        <v>113.5</v>
+      </c>
+      <c r="C172">
+        <v>376</v>
+      </c>
+      <c r="D172">
+        <v>926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
